--- a/exports/HDFCLIFE_full_report.xlsx
+++ b/exports/HDFCLIFE_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>2.76</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.55208333334</v>
+        <v>44580.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>667.5</v>
+        <v>655</v>
       </c>
       <c r="I2" t="n">
         <v>655.118135378454</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>0.75</v>
+        <v>-1.14</v>
       </c>
       <c r="L2" t="n">
-        <v>0.95</v>
+        <v>1.55</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="N2" t="n">
-        <v>0.96</v>
+        <v>1.66</v>
       </c>
       <c r="O2" t="n">
         <v>0.15</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>3.94</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44622.38541666666</v>
+        <v>44622.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>545.75</v>
+        <v>559.4</v>
       </c>
       <c r="I3" t="n">
         <v>557.9167830323626</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>16.68</v>
+        <v>14.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.67</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44624.55208333334</v>
+        <v>44627.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>522.75</v>
+        <v>509.3</v>
       </c>
       <c r="I4" t="n">
         <v>509.3419057437863</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.55</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>8.06</v>
+        <v>9.83</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6899999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="N4" t="n">
         <v>4.79</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>9.609999999999999</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44650.38541666666</v>
+        <v>44650.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>536.6</v>
+        <v>541.3</v>
       </c>
       <c r="I5" t="n">
         <v>537.9178921202999</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.36</v>
+        <v>-6.28</v>
       </c>
       <c r="L5" t="n">
-        <v>5.6</v>
+        <v>6.69</v>
       </c>
       <c r="M5" t="n">
         <v>1.69</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>5.45</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44670.38541666666</v>
+        <v>44670.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>559.55</v>
+        <v>542.95</v>
       </c>
       <c r="I6" t="n">
         <v>543.8212022657015</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>3.37</v>
+        <v>0.3</v>
       </c>
       <c r="L6" t="n">
         <v>1.46</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>7.95</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44679.55208333334</v>
+        <v>44680.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>571.3</v>
+        <v>591.5</v>
       </c>
       <c r="I7" t="n">
         <v>573.5960056805711</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.22</v>
+        <v>-8.94</v>
       </c>
       <c r="L7" t="n">
-        <v>6.02</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="M7" t="n">
         <v>0.93</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44699.55208333334</v>
+        <v>44700.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>549.45</v>
+        <v>531.5</v>
       </c>
       <c r="I8" t="n">
         <v>546.7316204380404</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>-7.11</v>
+        <v>-10.14</v>
       </c>
       <c r="L8" t="n">
-        <v>8.279999999999999</v>
+        <v>11.01</v>
       </c>
       <c r="M8" t="n">
         <v>2.37</v>
       </c>
       <c r="N8" t="n">
-        <v>3.09</v>
+        <v>3.63</v>
       </c>
       <c r="O8" t="n">
         <v>1.8</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>7.79</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44705.55208333334</v>
+        <v>44706.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>555</v>
+        <v>569</v>
       </c>
       <c r="I9" t="n">
         <v>567.4707937210704</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.42</v>
+        <v>-7.06</v>
       </c>
       <c r="L9" t="n">
-        <v>4.65</v>
+        <v>7.54</v>
       </c>
       <c r="M9" t="n">
         <v>0.85</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>6.8</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44725.55208333334</v>
+        <v>44726.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>583.1</v>
+        <v>574.75</v>
       </c>
       <c r="I10" t="n">
         <v>580.793687866606</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="L10" t="n">
         <v>2.11</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>5.65</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44770.55208333334</v>
+        <v>44771.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>535.5</v>
+        <v>543.2</v>
       </c>
       <c r="I11" t="n">
         <v>542.9222879969592</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K11" t="n">
-        <v>6.83</v>
+        <v>5.49</v>
       </c>
       <c r="L11" t="n">
         <v>1.93</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,25 +1247,25 @@
         <v>5</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44795.55208333334</v>
+        <v>44796.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>567</v>
+        <v>563.75</v>
       </c>
       <c r="I12" t="n">
         <v>566.3186579037657</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K12" t="n">
-        <v>4.38</v>
+        <v>3.78</v>
       </c>
       <c r="L12" t="n">
         <v>2.83</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05</v>
+        <v>1.23</v>
       </c>
       <c r="N12" t="n">
         <v>1.89</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>5.3</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44854.55208333334</v>
+        <v>44855.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>537.45</v>
+        <v>543.05</v>
       </c>
       <c r="I13" t="n">
         <v>542.1426978168921</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>58.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K13" t="n">
-        <v>4.67</v>
+        <v>3.67</v>
       </c>
       <c r="L13" t="n">
         <v>7.32</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>3.88</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44903.55208333334</v>
+        <v>44904.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>576.4</v>
+        <v>574.7</v>
       </c>
       <c r="I14" t="n">
         <v>575.3202083218222</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K14" t="n">
-        <v>6.14</v>
+        <v>5.83</v>
       </c>
       <c r="L14" t="n">
         <v>3.31</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>3.84</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44928.55208333334</v>
+        <v>44929.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>569</v>
+        <v>596.5</v>
       </c>
       <c r="I15" t="n">
         <v>582.6505697586348</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K15" t="n">
-        <v>0.99</v>
+        <v>-3.79</v>
       </c>
       <c r="L15" t="n">
-        <v>2.64</v>
+        <v>4.36</v>
       </c>
       <c r="M15" t="n">
         <v>0.95</v>
       </c>
       <c r="N15" t="n">
-        <v>1.49</v>
+        <v>4.78</v>
       </c>
       <c r="O15" t="n">
         <v>0.49</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.51</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44950.55208333334</v>
+        <v>44951.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>590</v>
+        <v>584.95</v>
       </c>
       <c r="I16" t="n">
         <v>585.6770453121335</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.09</v>
+        <v>-1.94</v>
       </c>
       <c r="L16" t="n">
         <v>4.53</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>4.31</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44966.55208333334</v>
+        <v>44967.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>519.7</v>
+        <v>524.5</v>
       </c>
       <c r="I17" t="n">
         <v>520.8452573856673</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K17" t="n">
-        <v>11.15</v>
+        <v>10.33</v>
       </c>
       <c r="L17" t="n">
         <v>1.53</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>7.3</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44979.55208333334</v>
+        <v>44980.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>493.95</v>
+        <v>488.7</v>
       </c>
       <c r="I18" t="n">
         <v>489.3995252983432</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.82</v>
+        <v>-6.83</v>
       </c>
       <c r="L18" t="n">
-        <v>6.1</v>
+        <v>7.01</v>
       </c>
       <c r="M18" t="n">
         <v>0.24</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>6.28</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45006.55208333334</v>
+        <v>45007.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>483</v>
+        <v>496.55</v>
       </c>
       <c r="I19" t="n">
         <v>485.4763891344462</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K19" t="n">
-        <v>1.17</v>
+        <v>-1.61</v>
       </c>
       <c r="L19" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="M19" t="n">
         <v>0.64</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>6.84</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45037.38541666666</v>
+        <v>45037.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>518.6</v>
+        <v>513.5</v>
       </c>
       <c r="I20" t="n">
         <v>514.4863789694116</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>30</v>
+        <v>30.16666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>4.44</v>
+        <v>3.41</v>
       </c>
       <c r="L20" t="n">
         <v>2.98</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>5.35</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45040.38541666666</v>
+        <v>45040.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>535.35</v>
+        <v>547.1</v>
       </c>
       <c r="I21" t="n">
         <v>540.9605595567052</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.26</v>
+        <v>-6.54</v>
       </c>
       <c r="L21" t="n">
         <v>7.91</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>7.51</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45135.55208333334</v>
+        <v>45138.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>658.4</v>
+        <v>646.4</v>
       </c>
       <c r="I22" t="n">
         <v>647.9451181365212</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>95</v>
+        <v>97.83333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>20.34</v>
+        <v>18.15</v>
       </c>
       <c r="L22" t="n">
         <v>5.68</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>135</v>
+        <v>136</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>5.05</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45169.38541666666</v>
+        <v>45169.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>640.65</v>
+        <v>646.05</v>
       </c>
       <c r="I23" t="n">
         <v>644.4233939864168</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>0.89</v>
+        <v>0.05</v>
       </c>
       <c r="L23" t="n">
         <v>1.33</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>3.83</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45194.38541666666</v>
+        <v>45194.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>645.2</v>
+        <v>643</v>
       </c>
       <c r="I24" t="n">
         <v>643.8275094475848</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>24.83333333333333</v>
+        <v>25</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.13</v>
+        <v>-0.47</v>
       </c>
       <c r="L24" t="n">
         <v>1.87</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>4.36</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45217.38541666666</v>
+        <v>45217.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>641.3</v>
+        <v>644.4</v>
       </c>
       <c r="I25" t="n">
         <v>642.9696020708604</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>22.83333333333333</v>
+        <v>23</v>
       </c>
       <c r="K25" t="n">
-        <v>0.26</v>
+        <v>-0.22</v>
       </c>
       <c r="L25" t="n">
         <v>1.19</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>4.11</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45222.55208333334</v>
+        <v>45224.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>625</v>
+        <v>608.55</v>
       </c>
       <c r="I26" t="n">
         <v>617.9060455415773</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>5</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.01</v>
+        <v>-5.56</v>
       </c>
       <c r="L26" t="n">
-        <v>3.51</v>
+        <v>5.64</v>
       </c>
       <c r="M26" t="n">
         <v>0.84</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>6.86</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45245.55208333334</v>
+        <v>45246.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>635.95</v>
+        <v>638.5</v>
       </c>
       <c r="I27" t="n">
         <v>637.3737533667559</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.5</v>
+        <v>-4.92</v>
       </c>
       <c r="L27" t="n">
-        <v>5.07</v>
+        <v>5.08</v>
       </c>
       <c r="M27" t="n">
         <v>1.6</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>3.95</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45279.38541666666</v>
+        <v>45279.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>669.9</v>
+        <v>666.6</v>
       </c>
       <c r="I28" t="n">
         <v>667.6731411388462</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K28" t="n">
-        <v>4.92</v>
+        <v>4.4</v>
       </c>
       <c r="L28" t="n">
         <v>1.02</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>4.84</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45328.55208333334</v>
+        <v>45329.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>592.2</v>
+        <v>605.65</v>
       </c>
       <c r="I29" t="n">
         <v>594.8959114663002</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>49</v>
+        <v>49.83333333333334</v>
       </c>
       <c r="K29" t="n">
-        <v>11.16</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="L29" t="n">
         <v>1.11</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>6.05</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45343.55208333334</v>
+        <v>45344.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>577.8</v>
+        <v>570.15</v>
       </c>
       <c r="I30" t="n">
         <v>573.2231754882645</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.6</v>
+        <v>-5.86</v>
       </c>
       <c r="L30" t="n">
-        <v>5.49</v>
+        <v>6.37</v>
       </c>
       <c r="M30" t="n">
         <v>1.29</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>5.29</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45352.38541666666</v>
+        <v>45355.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>590.35</v>
+        <v>615.35</v>
       </c>
       <c r="I31" t="n">
         <v>599.9052809928307</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.54</v>
+        <v>-7.93</v>
       </c>
       <c r="L31" t="n">
-        <v>3.83</v>
+        <v>8.17</v>
       </c>
       <c r="M31" t="n">
-        <v>0.15</v>
+        <v>0.79</v>
       </c>
       <c r="N31" t="n">
-        <v>1.09</v>
+        <v>3.16</v>
       </c>
       <c r="O31" t="n">
         <v>-0.16</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>7.44</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45397.55208333334</v>
+        <v>45398.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>614.95</v>
+        <v>605.25</v>
       </c>
       <c r="I32" t="n">
         <v>613.4571168393395</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.64</v>
       </c>
       <c r="L32" t="n">
         <v>4.51</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>4.3</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45425.38541666666</v>
+        <v>45425.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>560.1</v>
+        <v>568.2</v>
       </c>
       <c r="I33" t="n">
         <v>566.3137249137161</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>7.46</v>
+        <v>6.12</v>
       </c>
       <c r="L33" t="n">
         <v>3.1</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,25 +2765,25 @@
         <v>5.78</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45441.55208333334</v>
+        <v>45442.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>561.7</v>
+        <v>554.5</v>
       </c>
       <c r="I34" t="n">
         <v>554.9990414498345</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.14</v>
+        <v>-2.41</v>
       </c>
       <c r="L34" t="n">
         <v>3.08</v>
       </c>
       <c r="M34" t="n">
-        <v>0.43</v>
+        <v>1.59</v>
       </c>
       <c r="N34" t="n">
         <v>2.82</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>5.06</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45450.55208333334</v>
+        <v>45453.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>562.85</v>
+        <v>571.85</v>
       </c>
       <c r="I35" t="n">
         <v>570.228352004649</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K35" t="n">
-        <v>-1.51</v>
+        <v>-3.13</v>
       </c>
       <c r="L35" t="n">
-        <v>2.66</v>
+        <v>3.26</v>
       </c>
       <c r="M35" t="n">
         <v>3.73</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>6.25</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45544.55208333334</v>
+        <v>45545.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>734.95</v>
+        <v>709.5</v>
       </c>
       <c r="I36" t="n">
         <v>727.3220148666551</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>91.16666666666667</v>
+        <v>92</v>
       </c>
       <c r="K36" t="n">
-        <v>28.52</v>
+        <v>24.07</v>
       </c>
       <c r="L36" t="n">
         <v>1.84</v>
@@ -2493,7 +2924,7 @@
         <v>3.07</v>
       </c>
       <c r="N36" t="n">
-        <v>4.01</v>
+        <v>4.29</v>
       </c>
       <c r="O36" t="n">
         <v>0.9</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>6.49</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45555.55208333334</v>
+        <v>45558.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>713</v>
+        <v>724.7</v>
       </c>
       <c r="I37" t="n">
         <v>724.4792643966512</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.49</v>
+        <v>-2.14</v>
       </c>
       <c r="L37" t="n">
         <v>3.19</v>
       </c>
       <c r="M37" t="n">
-        <v>0.55</v>
+        <v>0.82</v>
       </c>
       <c r="N37" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="O37" t="n">
         <v>-4.29</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>4.96</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45589.55208333334</v>
+        <v>45590.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>716.45</v>
+        <v>707.65</v>
       </c>
       <c r="I38" t="n">
         <v>711.4095949022924</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.14</v>
+        <v>-2.35</v>
       </c>
       <c r="L38" t="n">
         <v>3.89</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>5.81</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>593.7</v>
+        <v>642.8</v>
       </c>
       <c r="I39" t="n">
         <v>619.7354733204869</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>82.16666666666667</v>
+        <v>83</v>
       </c>
       <c r="K39" t="n">
-        <v>16.1</v>
+        <v>9.16</v>
       </c>
       <c r="L39" t="n">
         <v>5.29</v>
       </c>
       <c r="M39" t="n">
-        <v>2.27</v>
+        <v>6.13</v>
       </c>
       <c r="N39" t="n">
-        <v>3.11</v>
+        <v>8.08</v>
       </c>
       <c r="O39" t="n">
         <v>-0.9</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>6.52</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45688.55208333334</v>
+        <v>45689.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>638.85</v>
+        <v>599.85</v>
       </c>
       <c r="I40" t="n">
         <v>606.1928085030208</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.61</v>
+        <v>-6.68</v>
       </c>
       <c r="L40" t="n">
-        <v>6.64</v>
+        <v>7.4</v>
       </c>
       <c r="M40" t="n">
         <v>0.55</v>
       </c>
       <c r="N40" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="O40" t="n">
         <v>8.08</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>13.55</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45727.38541666666</v>
+        <v>45727.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>632.6</v>
+        <v>636.5</v>
       </c>
       <c r="I41" t="n">
         <v>636.48771957641</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>38</v>
+        <v>38.16666666666666</v>
       </c>
       <c r="K41" t="n">
-        <v>-5.46</v>
+        <v>-6.11</v>
       </c>
       <c r="L41" t="n">
         <v>11.29</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>4.75</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>685.9</v>
+        <v>656.9</v>
       </c>
       <c r="I42" t="n">
         <v>663.0933894278155</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>24</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>7.76</v>
+        <v>3.21</v>
       </c>
       <c r="L42" t="n">
         <v>2.68</v>
       </c>
       <c r="M42" t="n">
-        <v>0.79</v>
+        <v>3.23</v>
       </c>
       <c r="N42" t="n">
-        <v>1.76</v>
+        <v>2.72</v>
       </c>
       <c r="O42" t="n">
         <v>2.09</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>7.16</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>685.35</v>
+        <v>704.6</v>
       </c>
       <c r="I43" t="n">
         <v>701.4746851040924</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.33</v>
+        <v>-7.26</v>
       </c>
       <c r="L43" t="n">
-        <v>5.28</v>
+        <v>7.7</v>
       </c>
       <c r="M43" t="n">
         <v>1.09</v>
       </c>
       <c r="N43" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="O43" t="n">
         <v>-2.72</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>5.92</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45810.55208333334</v>
+        <v>45811.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>765</v>
+        <v>756.75</v>
       </c>
       <c r="I44" t="n">
         <v>762.4252981945453</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K44" t="n">
-        <v>8.57</v>
+        <v>7.4</v>
       </c>
       <c r="L44" t="n">
         <v>2.03</v>
       </c>
       <c r="M44" t="n">
-        <v>1.26</v>
+        <v>2.17</v>
       </c>
       <c r="N44" t="n">
         <v>2.48</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>4.29</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45827.55208333334</v>
+        <v>45828.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>761.15</v>
+        <v>780.45</v>
       </c>
       <c r="I45" t="n">
         <v>779.0410445025676</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.58</v>
+        <v>-3.13</v>
       </c>
       <c r="L45" t="n">
-        <v>2.79</v>
+        <v>3.2</v>
       </c>
       <c r="M45" t="n">
         <v>0.55</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>5.67</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45847.55208333334</v>
+        <v>45848.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>785.1</v>
+        <v>773.6</v>
       </c>
       <c r="I46" t="n">
         <v>782.2159065214418</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K46" t="n">
-        <v>0.6</v>
+        <v>-0.88</v>
       </c>
       <c r="L46" t="n">
         <v>2.88</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>4.42</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45880.55208333334</v>
+        <v>45881.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>765</v>
+        <v>768.6</v>
       </c>
       <c r="I47" t="n">
         <v>765.2705342826109</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K47" t="n">
-        <v>1.11</v>
+        <v>0.65</v>
       </c>
       <c r="L47" t="n">
         <v>1.86</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>4.12</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45903.55208333334</v>
+        <v>45904.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>777.25</v>
+        <v>761.65</v>
       </c>
       <c r="I48" t="n">
         <v>770.5092981719271</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K48" t="n">
-        <v>1.13</v>
+        <v>-0.9</v>
       </c>
       <c r="L48" t="n">
         <v>1.33</v>
@@ -3177,7 +3752,7 @@
         <v>0.45</v>
       </c>
       <c r="N48" t="n">
-        <v>2.01</v>
+        <v>2.92</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>7.98</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45971.55208333334</v>
+        <v>45972.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>750.05</v>
+        <v>761</v>
       </c>
       <c r="I49" t="n">
         <v>760.4447367873247</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>67.16666666666667</v>
+        <v>68</v>
       </c>
       <c r="K49" t="n">
-        <v>1.52</v>
+        <v>0.09</v>
       </c>
       <c r="L49" t="n">
         <v>5.43</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>4.66</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45992.55208333334</v>
+        <v>45993.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>765</v>
+        <v>757.45</v>
       </c>
       <c r="I50" t="n">
         <v>760.7362070343012</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K50" t="n">
-        <v>0.53</v>
+        <v>-0.47</v>
       </c>
       <c r="L50" t="n">
         <v>1.79</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>4.09</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46003.38541666666</v>
+        <v>46003.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>772.3</v>
+        <v>778.95</v>
       </c>
       <c r="I51" t="n">
         <v>777.3210629563698</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.96</v>
+        <v>-2.84</v>
       </c>
       <c r="L51" t="n">
         <v>2.96</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>4.29</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46020.55208333334</v>
+        <v>46021.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>746.75</v>
+        <v>737.1</v>
       </c>
       <c r="I52" t="n">
         <v>745.594357416334</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>-4.13</v>
+        <v>-5.37</v>
       </c>
       <c r="L52" t="n">
-        <v>4.72</v>
+        <v>5.42</v>
       </c>
       <c r="M52" t="n">
         <v>0.83</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>4.07</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46027.55208333334</v>
+        <v>46028.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>760.6</v>
+        <v>777</v>
       </c>
       <c r="I53" t="n">
         <v>767.1111184073162</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.19</v>
+        <v>-5.41</v>
       </c>
       <c r="L53" t="n">
-        <v>3.84</v>
+        <v>5.81</v>
       </c>
       <c r="M53" t="n">
         <v>0.02</v>
       </c>
       <c r="N53" t="n">
-        <v>0.98</v>
+        <v>2.03</v>
       </c>
       <c r="O53" t="n">
         <v>0.2</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>5.02</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46034.55208333334</v>
+        <v>46035.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>754.65</v>
+        <v>748.15</v>
       </c>
       <c r="I54" t="n">
         <v>749.6397212334418</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.88</v>
+        <v>-3.71</v>
       </c>
       <c r="L54" t="n">
-        <v>3.77</v>
+        <v>4.43</v>
       </c>
       <c r="M54" t="n">
         <v>0.84</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>4.07</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46070.55208333334</v>
+        <v>46071.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>705</v>
+        <v>723.3</v>
       </c>
       <c r="I55" t="n">
         <v>720.1713603388055</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K55" t="n">
-        <v>5.77</v>
+        <v>3.32</v>
       </c>
       <c r="L55" t="n">
         <v>1.28</v>
@@ -3576,7 +4235,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="N55" t="n">
-        <v>1.78</v>
+        <v>3.5</v>
       </c>
       <c r="O55" t="n">
         <v>-0.62</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,25 +4283,25 @@
         <v>5.11</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>716.75</v>
+        <v>704.9</v>
       </c>
       <c r="I56" t="n">
         <v>714.9326721370882</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.91</v>
+        <v>-2.54</v>
       </c>
       <c r="L56" t="n">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
       <c r="M56" t="n">
-        <v>0.39</v>
+        <v>1.7</v>
       </c>
       <c r="N56" t="n">
         <v>2.25</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>5.33</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>579.15</v>
+        <v>606</v>
       </c>
       <c r="I57" t="n">
         <v>600.8955504181105</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K57" t="n">
-        <v>17.84</v>
+        <v>14.03</v>
       </c>
       <c r="L57" t="n">
         <v>2.14</v>
       </c>
       <c r="M57" t="n">
-        <v>1.19</v>
+        <v>2.74</v>
       </c>
       <c r="N57" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="O57" t="n">
         <v>-1.35</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>7.47</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46135.38541666666</v>
+        <v>46135.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>604</v>
+        <v>597.5</v>
       </c>
       <c r="I58" t="n">
         <v>601.8209521132947</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.33</v>
+        <v>-1.4</v>
       </c>
       <c r="L58" t="n">
         <v>3.56</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>5.74</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46148.55208333334</v>
+        <v>46149.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>607.55</v>
+        <v>625.3</v>
       </c>
       <c r="I59" t="n">
         <v>616.9212623635447</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.68</v>
+        <v>-4.65</v>
       </c>
       <c r="L59" t="n">
-        <v>2.53</v>
+        <v>5.32</v>
       </c>
       <c r="M59" t="n">
         <v>1.28</v>
       </c>
       <c r="N59" t="n">
-        <v>2.11</v>
+        <v>3.2</v>
       </c>
       <c r="O59" t="n">
         <v>-1.11</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>6.56</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46171.38541666666</v>
+        <v>46171.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>603</v>
+        <v>596.45</v>
       </c>
       <c r="I60" t="n">
         <v>598.9211832377541</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.57</v>
+        <v>-4.61</v>
       </c>
       <c r="L60" t="n">
-        <v>5</v>
+        <v>5.84</v>
       </c>
       <c r="M60" t="n">
         <v>1.44</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>4.32</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46188.38541666666</v>
+        <v>46188.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>572.45</v>
+        <v>581.55</v>
       </c>
       <c r="I61" t="n">
         <v>573.2166005460367</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>16.83333333333333</v>
+        <v>17</v>
       </c>
       <c r="K61" t="n">
-        <v>4.02</v>
+        <v>2.5</v>
       </c>
       <c r="L61" t="n">
         <v>1.46</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>5.86</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46202.55208333334</v>
+        <v>46203.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>583.65</v>
+        <v>575.85</v>
       </c>
       <c r="I62" t="n">
         <v>576.1231483450334</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K62" t="n">
-        <v>0.36</v>
+        <v>-0.98</v>
       </c>
       <c r="L62" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="M62" t="n">
         <v>0.88</v>
       </c>
       <c r="N62" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="O62" t="n">
         <v>4.6</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>4.81</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46255.38541666666</v>
+        <v>46255.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>549.65</v>
+        <v>553</v>
       </c>
       <c r="I63" t="n">
         <v>552.1125475398122</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>52</v>
+        <v>52.16666666666666</v>
       </c>
       <c r="K63" t="n">
-        <v>4.55</v>
+        <v>3.97</v>
       </c>
       <c r="L63" t="n">
         <v>2.11</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>3.45</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46266.55208333334</v>
+        <v>46267.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>540.85</v>
+        <v>537.05</v>
       </c>
       <c r="I64" t="n">
         <v>538.1645192378506</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.2</v>
+        <v>-2.88</v>
       </c>
       <c r="L64" t="n">
-        <v>2.82</v>
+        <v>3.79</v>
       </c>
       <c r="M64" t="n">
         <v>0.83</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>3.22</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46281.55208333334</v>
+        <v>46282.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>530.2</v>
+        <v>558.6</v>
       </c>
       <c r="I65" t="n">
         <v>540.8025741855771</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K65" t="n">
-        <v>1.28</v>
+        <v>-4.01</v>
       </c>
       <c r="L65" t="n">
-        <v>2.04</v>
+        <v>4.38</v>
       </c>
       <c r="M65" t="n">
         <v>0.61</v>
       </c>
       <c r="N65" t="n">
-        <v>2.29</v>
+        <v>5.05</v>
       </c>
       <c r="O65" t="n">
         <v>-1.08</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>8.31</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46288.55208333334</v>
+        <v>46289.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>562.65</v>
+        <v>533</v>
       </c>
       <c r="I66" t="n">
         <v>538.809364542127</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K66" t="n">
-        <v>0.73</v>
+        <v>-4.58</v>
       </c>
       <c r="L66" t="n">
-        <v>5.13</v>
+        <v>7.98</v>
       </c>
       <c r="M66" t="n">
-        <v>0.44</v>
+        <v>5.63</v>
       </c>
       <c r="N66" t="n">
-        <v>0.52</v>
+        <v>5.94</v>
       </c>
       <c r="O66" t="n">
         <v>5.05</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>5.4</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46302.38541666666</v>
+        <v>46302.55208333334</v>
       </c>
       <c r="H67" t="n">
-        <v>542.25</v>
+        <v>547.75</v>
       </c>
       <c r="I67" t="n">
         <v>545.6969842022139</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K67" t="n">
-        <v>-1.74</v>
+        <v>-2.77</v>
       </c>
       <c r="L67" t="n">
         <v>3.45</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>6.58</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46316.55208333334</v>
+        <v>46317.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>534.65</v>
+        <v>526.65</v>
       </c>
       <c r="I68" t="n">
         <v>532.6005278616948</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.39</v>
+        <v>-3.85</v>
       </c>
       <c r="L68" t="n">
-        <v>2.95</v>
+        <v>3.98</v>
       </c>
       <c r="M68" t="n">
         <v>0.48</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,12 @@
       <c r="Q69" t="n">
         <v>8</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6479,7 +7312,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.1</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="6">
@@ -6489,7 +7322,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -6499,7 +7332,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="8">
@@ -6509,7 +7342,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -6519,7 +7352,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31.7</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="10">
@@ -6529,7 +7362,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48.5</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="11">
@@ -6539,7 +7372,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
@@ -6549,7 +7382,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -6559,7 +7392,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>71.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -6569,7 +7402,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.68</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="15">
@@ -6579,7 +7412,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.39</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="16">
@@ -6589,7 +7422,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.98</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="17">
@@ -6599,7 +7432,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28.52</v>
+        <v>24.07</v>
       </c>
     </row>
     <row r="18">
@@ -6609,7 +7442,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50.7</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +7452,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.54</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="20">
@@ -6629,7 +7462,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.96</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="21">
@@ -6649,7 +7482,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
@@ -6659,7 +7492,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -6669,7 +7502,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="25">
@@ -6689,7 +7522,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.66</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="27">
@@ -6699,7 +7532,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.96</v>
+        <v>8.08</v>
       </c>
     </row>
     <row r="28">
@@ -6709,7 +7542,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
